--- a/public/inputs/y08-science - input.xlsx
+++ b/public/inputs/y08-science - input.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001D7A3D"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,24 +415,19 @@
   </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Section type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
@@ -459,9 +444,7 @@
           <t>Unit 1 · Respiration</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
